--- a/mockup_status.xlsx
+++ b/mockup_status.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>{"Item_Name": "Funny Pug T-Shirt Graphic T-Shirt Soft Cotton", "bullets": ["PREMIUM COMFORT: Made from soft, high-quality cotton for a comfortable fit", "UNIQUE DESIGN: Features a funny pug on a treadmill design that's sure to turn heads", "GREAT GIFT: Perfect for pug lovers, fitness enthusiasts, and anyone with a sense of humor", "DURABLE: Built to last with a sturdy construction that withstands repeated washing", "FUNNY STATEMENT: The phrase 'I've appeared. That's enough.' adds a humorous touch"], "description": "&lt;p&gt;Make a statement with this hilarious pug on a treadmill t-shirt! &lt;/p&gt;&lt;br&gt;&lt;p&gt;Featuring a fun design of a pug on a treadmill with the phrase 'I've appeared. That's enough.', this tee is perfect for anyone who loves pugs, fitness, or just a good laugh.&lt;/p&gt;&lt;br&gt;&lt;p&gt;Our soft, high-quality cotton t-shirts are built to last and provide all-day comfort. Whether you're running errands or lounging around, this funny tee is sure to bring a smile to your face and those around you.&lt;/p&gt;", "keywords": ["pug t shirt", "funny t shirts", "graphic t shirts", "soft cotton t shirts", "pug lover gifts", "fitness humor", "funny pug shirt", "treadmill pug tee", "humorous workout shirts"], "subject_character": "Pug", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819471/pod/IATE-Dog/IATE-Dog-b-1_nowobs.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819472/pod/IATE-Dog/IATE-Dog-b-2_wz0zk3.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819474/pod/IATE-Dog/IATE-Dog-b-3_e3abpw.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819476/pod/IATE-Dog/IATE-Dog-b-4_xneu43.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819477/pod/IATE-Dog/IATE-Dog-b-5_rzxyb7.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819479/pod/IATE-Dog/IATE-Dog-b-6_it92i5.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819481/pod/IATE-Dog/IATE-Dog-b-7_oo9j4j.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819483/pod/IATE-Dog/IATE-Dog-b-8_ky62hv.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819485/pod/IATE-Dog/IATE-Dog-w-1_prl3ra.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819486/pod/IATE-Dog/IATE-Dog-w-2_l2jmd4.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819488/pod/IATE-Dog/IATE-Dog-w-3_ctkv6b.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819489/pod/IATE-Dog/IATE-Dog-w-4_hqqfu9.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819491/pod/IATE-Dog/IATE-Dog-w-5_m9dzjo.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819493/pod/IATE-Dog/IATE-Dog-w-6_qdei4t.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819495/pod/IATE-Dog/IATE-Dog-w-7_t1gxcw.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774819497/pod/IATE-Dog/IATE-Dog-w-8_gvnvyc.png"]}</t>
+          <t>{"Item_Name": "Funny Pug T-Shirt Graphic Tee", "bullets": ["COMFORTABLE FIT: Made from high-quality, soft materials for a comfortable fit.", "FUNNY DESIGN: A humorous pug on a treadmill with a funny phrase.", "DURABLE: Long-lasting print and high-quality fabric.", "GREAT GIFT: Perfect for dog lovers and fitness enthusiasts.", "UNIQUE STYLE: Stand out with this one-of-a-kind design."], "description": "Get ready to turn heads with this hilarious pug t-shirt! Featuring a funny graphic of a pug on a treadmill with the phrase 'I've appeared. That's enough.', this tee is perfect for dog lovers and fitness enthusiasts alike. Made from high-quality, soft materials, this shirt is not only stylish but also comfortable to wear. The durable print and fabric ensure that it will remain a favorite for a long time. Whether you're looking for a unique gift or a fun addition to your own wardrobe, this pug t-shirt is sure to bring a smile to everyone's face.", "keywords": ["pug t shirt", "funny dog tee", "fitness humor", "pet lovers shirt", "treadmill pug", "comfy tees", "unique gifts", "dog graphic tee", "humorous apparel", "pug lover shirt"], "subject_character": "Pug", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820697/pod/IATE-Dog/IATE-Dog-b-1_ebhn0m.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820698/pod/IATE-Dog/IATE-Dog-b-2_fahwdd.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820699/pod/IATE-Dog/IATE-Dog-b-3_hmbpod.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820701/pod/IATE-Dog/IATE-Dog-b-4_xl0jr9.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820702/pod/IATE-Dog/IATE-Dog-b-5_n79yfm.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820704/pod/IATE-Dog/IATE-Dog-b-6_l88l4y.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820706/pod/IATE-Dog/IATE-Dog-b-7_qqlno4.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820708/pod/IATE-Dog/IATE-Dog-b-8_uqwx94.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820709/pod/IATE-Dog/IATE-Dog-w-1_ntcb0o.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820710/pod/IATE-Dog/IATE-Dog-w-2_j08b6d.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820712/pod/IATE-Dog/IATE-Dog-w-3_rxe3il.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820713/pod/IATE-Dog/IATE-Dog-w-4_kftrgj.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820715/pod/IATE-Dog/IATE-Dog-w-5_df342j.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820717/pod/IATE-Dog/IATE-Dog-w-6_iuhegw.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820719/pod/IATE-Dog/IATE-Dog-w-7_o3mywc.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1774820725/pod/IATE-Dog/IATE-Dog-w-8_dhk4p9.png"]}</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/mockup_status.xlsx
+++ b/mockup_status.xlsx
@@ -422,7 +422,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="93.86214285714286" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
     <col width="53.43357142857143" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
@@ -458,9 +458,9 @@
           <t>C:\Users\Admin\Downloads\Auto_download_mockup\Image_src\I've appeared that' enough\IATE-Rab</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>{"Item_Name": "Funny Rabbit T-Shirt Graphic Workout Bunny Cotton Tee", "bullets": ["PREMIUM COMFORT: Soft and breathable cotton for all-day wear", "UNIQUE GRAPHIC: Adorable rabbit design with a humorous workout twist", "DURABLE QUALITY: Long-lasting print and comfortable fit", "FUN FOR ALL: Perfect for fitness enthusiasts and animal lovers alike", "GREAT GIFT: Ideal for friends and family who love to laugh and workout"], "description": "Get ready to hop into fitness with our Funny Rabbit T-Shirt! This graphic tee features an adorable rabbit in a humorous workout setting, complete with a stationary bike, dumbbells, and a coffee cup. Made from soft and breathable cotton, this tee is perfect for anyone who loves to laugh and stay active. The unique design and durable quality make it a great addition to any wardrobe. Whether you're hitting the gym or just lounging around, this funny rabbit shirt is sure to bring a smile to your face.", "keywords": ["funny rabbit t-shirt", "graphic workout tee", "cotton t-shirt", "humorous fitness shirt", "workout bunny tee", "funny animal shirt", "exercise rabbit t-shirt", "gym tee", "fitness apparel", "humorous gift", "t-shirt for fitness enthusiasts"], "subject_character": "Rabbit", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316093/pod/IATE-Rab/IATE-Rab-b-1_yurz3m.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316094/pod/IATE-Rab/IATE-Rab-b-2_e9kvp4.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316095/pod/IATE-Rab/IATE-Rab-b-3_owscv8.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316096/pod/IATE-Rab/IATE-Rab-b-4_giwabx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316097/pod/IATE-Rab/IATE-Rab-b-5_xrk9ot.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316099/pod/IATE-Rab/IATE-Rab-b-6_vzb3j3.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316101/pod/IATE-Rab/IATE-Rab-b-7_luqe0d.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316103/pod/IATE-Rab/IATE-Rab-b-8_tbsps9.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316106/pod/IATE-Rab/IATE-Rab-w-1_k1hu5f.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316107/pod/IATE-Rab/IATE-Rab-w-2_kcngmy.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316108/pod/IATE-Rab/IATE-Rab-w-3_hzsmgx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316109/pod/IATE-Rab/IATE-Rab-w-4_pcbueb.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316110/pod/IATE-Rab/IATE-Rab-w-5_tbhfre.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316112/pod/IATE-Rab/IATE-Rab-w-6_gvigsf.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316114/pod/IATE-Rab/IATE-Rab-w-7_caxpyx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316116/pod/IATE-Rab/IATE-Rab-w-8_miktxp.png"]}</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>{"Item_Name": "Funny Rabbit Character Workout T-Shirt – “I've Appeared. That's enough.”, Heavy Cotton, Fitness Humor, For Gym Lovers, Casual Everyday Wear, Graphic Tee, Comfortable Fit, Trendy Statement Shirt", "bullets": ["PREMIUM COMFORT: Made from super-soft, heavy cotton for a comfortable fit that's perfect for lounging or working out.", "PERFECT GIFT: A hilarious and unique gift for fitness enthusiasts and humor lovers who appreciate a good laugh.", "UNIQUE DESIGN: Features an exclusive cartoon rabbit character with a humorous quote that's sure to turn heads.", "LIGHTWEIGHT FABRIC: Breathable and lightweight, making it ideal for everyday wear, whether you're hitting the gym or just running errands.", "VERSATILE STYLE: Pair it with your favorite leggings or jeans for a casual, stylish look that's perfect for any occasion."], "description": "Get ready to turn heads with this funny rabbit character workout t-shirt! Featuring a cartoon rabbit in shades and a cap, lounging on an exercise bike with the hilarious quote “I've Appeared. That's enough.” This tee is perfect for fitness enthusiasts and humor lovers alike. Made from super-soft, heavy cotton, it's not only comfortable but also durable. Whether you're heading to the gym or just running errands, this graphic tee is sure to make a statement. The unique design and humorous quote make it a great gift idea for friends or a treat for yourself. So why wait? Get your funny rabbit character workout t-shirt today and add some humor to your wardrobe!", "keywords": "funny quote t-shirt, rabbit character shirt, workout tee, fitness humor, gym shirt, casual wear, graphic t-shirt, comfortable fit, trendy statement shirt, humor gift, cartoon character tee, exercise shirt, everyday wear", "subject_character": "Funny Quote", "cloudinary_links": ["https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316093/pod/IATE-Rab/IATE-Rab-b-1_yurz3m.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316094/pod/IATE-Rab/IATE-Rab-b-2_e9kvp4.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316095/pod/IATE-Rab/IATE-Rab-b-3_owscv8.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316096/pod/IATE-Rab/IATE-Rab-b-4_giwabx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316097/pod/IATE-Rab/IATE-Rab-b-5_xrk9ot.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316099/pod/IATE-Rab/IATE-Rab-b-6_vzb3j3.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316101/pod/IATE-Rab/IATE-Rab-b-7_luqe0d.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316103/pod/IATE-Rab/IATE-Rab-b-8_tbsps9.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316106/pod/IATE-Rab/IATE-Rab-w-1_k1hu5f.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316107/pod/IATE-Rab/IATE-Rab-w-2_kcngmy.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316108/pod/IATE-Rab/IATE-Rab-w-3_hzsmgx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316109/pod/IATE-Rab/IATE-Rab-w-4_pcbueb.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316110/pod/IATE-Rab/IATE-Rab-w-5_tbhfre.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316112/pod/IATE-Rab/IATE-Rab-w-6_gvigsf.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316114/pod/IATE-Rab/IATE-Rab-w-7_caxpyx.png", "https://res.cloudinary.com/dex1n6s6f/image/upload/v1775316116/pod/IATE-Rab/IATE-Rab-w-8_miktxp.png"]}</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -468,14 +468,14 @@
           <t>done</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr"/>
+      <c r="A3" s="3" t="n"/>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="inlineStr">
